--- a/output/yearly_surface_area_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_10_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630272806</v>
+        <v>10.84497649741</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907183916271</v>
+        <v>37.7890725175275</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.482480091141689</v>
+        <v>5.855143308127976</v>
       </c>
       <c r="C2" t="n">
-        <v>11.02797196180442</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="D2" t="n">
-        <v>20.61081130295754</v>
+        <v>34.15303913533804</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.96674375124262</v>
+        <v>19.3747909433108</v>
       </c>
       <c r="C3" t="n">
-        <v>24.25898577193868</v>
+        <v>26.50718801466388</v>
       </c>
       <c r="D3" t="n">
-        <v>61.47213250141404</v>
+        <v>72.07009896875836</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.28517416478385</v>
+        <v>37.34371917414018</v>
       </c>
       <c r="C4" t="n">
-        <v>64.66870302644165</v>
+        <v>69.14841780091984</v>
       </c>
       <c r="D4" t="n">
-        <v>84.47644470732529</v>
+        <v>75.01926907231577</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.66952054322988</v>
+        <v>49.72552122010096</v>
       </c>
       <c r="C5" t="n">
-        <v>102.0281301638498</v>
+        <v>119.5523266846554</v>
       </c>
       <c r="D5" t="n">
-        <v>67.71604790042376</v>
+        <v>52.40078371417351</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.91455655866408</v>
+        <v>43.99505987041232</v>
       </c>
       <c r="C6" t="n">
-        <v>122.5662921366931</v>
+        <v>149.4946499164788</v>
       </c>
       <c r="D6" t="n">
-        <v>46.57116584635595</v>
+        <v>40.89568236810514</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.08115056874977</v>
+        <v>29.2845522699781</v>
       </c>
       <c r="C7" t="n">
-        <v>113.7246723122463</v>
+        <v>146.0035550801771</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.77315952705676</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>80.52785544084462</v>
+        <v>102.9755166984479</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>55.02499532762521</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.680384374164086</v>
+        <v>7.660716339345377</v>
       </c>
       <c r="C21" t="n">
-        <v>93.12466053673953</v>
+        <v>92.88618561456269</v>
       </c>
       <c r="D21" t="n">
-        <v>7.680384374164086</v>
+        <v>7.660716339345377</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.145159791508286</v>
+        <v>7.299294181075035</v>
       </c>
       <c r="C2" t="n">
-        <v>14.02132071205295</v>
+        <v>11.9272528588945</v>
       </c>
       <c r="D2" t="n">
-        <v>24.73709690390688</v>
+        <v>28.78582443622073</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.28505099159684</v>
+        <v>19.27170743436489</v>
       </c>
       <c r="C3" t="n">
-        <v>33.69848994827176</v>
+        <v>36.45720099720531</v>
       </c>
       <c r="D3" t="n">
-        <v>62.99384144299659</v>
+        <v>79.97316798794517</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.93683365622549</v>
+        <v>36.56519324467246</v>
       </c>
       <c r="C4" t="n">
-        <v>61.92471819307181</v>
+        <v>66.92770449391357</v>
       </c>
       <c r="D4" t="n">
-        <v>94.20163746559419</v>
+        <v>89.2752274856837</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.97662764820988</v>
+        <v>52.79348279587224</v>
       </c>
       <c r="C5" t="n">
-        <v>110.3975293425539</v>
+        <v>123.11116211255</v>
       </c>
       <c r="D5" t="n">
-        <v>79.54610773659782</v>
+        <v>64.91806694332035</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.52211951887262</v>
+        <v>53.89696721544566</v>
       </c>
       <c r="C6" t="n">
-        <v>140.3575240330538</v>
+        <v>166.7223586306019</v>
       </c>
       <c r="D6" t="n">
-        <v>55.82904669740338</v>
+        <v>46.41015922285948</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.26187426178919</v>
+        <v>39.34550274309942</v>
       </c>
       <c r="C7" t="n">
-        <v>144.5662764411598</v>
+        <v>178.8813039476985</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>40.66300816219864</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.45042657426681</v>
+        <v>22.03041848329842</v>
       </c>
       <c r="C8" t="n">
-        <v>113.2396889463483</v>
+        <v>143.1977201414398</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>72.1093688769282</v>
+        <v>87.86249253927252</v>
       </c>
       <c r="D9" t="n">
         <v>35.38905949498476</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.861341203316725</v>
+        <v>7.832510766935026</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2147679927028</v>
+        <v>100.8435761242884</v>
       </c>
       <c r="D21" t="n">
-        <v>8.844008853731316</v>
+        <v>8.811574612801904</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.405143006684444</v>
+        <v>7.728317927830891</v>
       </c>
       <c r="C2" t="n">
-        <v>14.80573712774615</v>
+        <v>10.52433538952581</v>
       </c>
       <c r="D2" t="n">
-        <v>21.66128134650162</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.51852701875834</v>
+        <v>21.01921834792421</v>
       </c>
       <c r="C3" t="n">
-        <v>43.26562132615694</v>
+        <v>40.938879267092</v>
       </c>
       <c r="D3" t="n">
-        <v>66.62630794870978</v>
+        <v>82.52571201898689</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.9961394291078</v>
+        <v>35.60798923303181</v>
       </c>
       <c r="C4" t="n">
-        <v>71.98174167537614</v>
+        <v>76.38488012892309</v>
       </c>
       <c r="D4" t="n">
-        <v>102.025184920737</v>
+        <v>103.6460503804485</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.53484118129882</v>
+        <v>53.16163818496479</v>
       </c>
       <c r="C5" t="n">
-        <v>110.6920536538279</v>
+        <v>121.6139968635737</v>
       </c>
       <c r="D5" t="n">
-        <v>90.98346849107317</v>
+        <v>76.64995200906974</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.03659637362695</v>
+        <v>60.53849043467533</v>
       </c>
       <c r="C6" t="n">
-        <v>154.4858552448696</v>
+        <v>177.4695507489917</v>
       </c>
       <c r="D6" t="n">
-        <v>65.81145735418494</v>
+        <v>53.85671555957153</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.58611304609789</v>
+        <v>49.1669067763845</v>
       </c>
       <c r="C7" t="n">
-        <v>170.9163848231442</v>
+        <v>205.8901650392326</v>
       </c>
       <c r="D7" t="n">
-        <v>47.25053525769474</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.87873061522568</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="C8" t="n">
-        <v>146.6191108907399</v>
+        <v>181.1668126031851</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.19531103988288</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>101.9515538429185</v>
+        <v>124.0281144683165</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>60.35784885709391</v>
+        <v>69.89552780385168</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>41.22554959673205</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.026420358787165</v>
+        <v>7.988025402656631</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3599773884751</v>
+        <v>107.8383429358645</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03302544848396</v>
+        <v>9.98503175332079</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.406705591465437</v>
+        <v>7.157922511663494</v>
       </c>
       <c r="C2" t="n">
-        <v>10.06782270705104</v>
+        <v>7.324819621385452</v>
       </c>
       <c r="D2" t="n">
-        <v>17.84031928157304</v>
+        <v>27.76480682380404</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.59139733305085</v>
+        <v>24.74004214701962</v>
       </c>
       <c r="C3" t="n">
-        <v>61.58012474888118</v>
+        <v>57.46169312956582</v>
       </c>
       <c r="D3" t="n">
-        <v>73.45436323174634</v>
+        <v>87.50808161803945</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.34752299177014</v>
+        <v>25.53820303057228</v>
       </c>
       <c r="C4" t="n">
-        <v>95.32475683925254</v>
+        <v>101.0296927486308</v>
       </c>
       <c r="D4" t="n">
-        <v>99.29396280752239</v>
+        <v>95.20989235785567</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.12769362147687</v>
+        <v>34.09118902997049</v>
       </c>
       <c r="C5" t="n">
-        <v>92.30882789180636</v>
+        <v>106.0287520586555</v>
       </c>
       <c r="D5" t="n">
-        <v>63.76451339083034</v>
+        <v>52.76893910326607</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>30.51075515258238</v>
       </c>
       <c r="C6" t="n">
-        <v>112.5436298240374</v>
+        <v>135.6078286399077</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>28.57867567062465</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>103.0648557395344</v>
+        <v>127.3788193829109</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>27.36818075128833</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>75.10369937488099</v>
+        <v>91.37616757277186</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>46.03905859065416</v>
+        <v>53.36093296892687</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.898921044191584</v>
+        <v>4.384485247166255</v>
       </c>
       <c r="C2" t="n">
-        <v>4.488550503816417</v>
+        <v>4.070325981807276</v>
       </c>
       <c r="D2" t="n">
-        <v>12.44659739444106</v>
+        <v>19.35221074611313</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.71335503255571</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="C3" t="n">
-        <v>51.27668259281091</v>
+        <v>43.88412237983243</v>
       </c>
       <c r="D3" t="n">
-        <v>71.36324062170064</v>
+        <v>90.28642762105792</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.04719030972863</v>
+        <v>34.61249706092554</v>
       </c>
       <c r="C4" t="n">
-        <v>125.9297597714426</v>
+        <v>124.6279623156114</v>
       </c>
       <c r="D4" t="n">
-        <v>112.2608864852143</v>
+        <v>113.1925650565445</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.97476196379262</v>
+        <v>37.74819922828986</v>
       </c>
       <c r="C5" t="n">
-        <v>132.3641342250762</v>
+        <v>143.6296891313084</v>
       </c>
       <c r="D5" t="n">
-        <v>78.9079717288374</v>
+        <v>67.17608666308801</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>35.98498035146259</v>
       </c>
       <c r="C6" t="n">
-        <v>131.7034180201181</v>
+        <v>155.0896300829814</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.60099382591507</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>129.7742837812731</v>
+        <v>157.5017841923158</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>97.63480918734528</v>
+        <v>117.3286681345363</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>57.35468262980289</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.25685804561417</v>
+        <v>4.414919425997907</v>
       </c>
       <c r="C2" t="n">
-        <v>9.745809460058087</v>
+        <v>6.129050917612838</v>
       </c>
       <c r="D2" t="n">
-        <v>13.18683516344316</v>
+        <v>17.94045754740621</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.853703896534</v>
+        <v>20.11601046001715</v>
       </c>
       <c r="C3" t="n">
-        <v>33.45305302221006</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D3" t="n">
-        <v>65.32549224058276</v>
+        <v>85.09789100411354</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.91728081759857</v>
+        <v>40.98109441837461</v>
       </c>
       <c r="C4" t="n">
-        <v>126.9252519435489</v>
+        <v>117.0724319837279</v>
       </c>
       <c r="D4" t="n">
-        <v>120.7991462690488</v>
+        <v>129.5798977358322</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.15977250054753</v>
+        <v>43.98229715025711</v>
       </c>
       <c r="C5" t="n">
-        <v>182.5314419120882</v>
+        <v>183.9549760832461</v>
       </c>
       <c r="D5" t="n">
-        <v>97.53663441692063</v>
+        <v>88.23457491918209</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.861722109084</v>
+        <v>42.38499363544755</v>
       </c>
       <c r="C6" t="n">
-        <v>168.131166586196</v>
+        <v>189.9073124140945</v>
       </c>
       <c r="D6" t="n">
-        <v>51.20010627187966</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="C7" t="n">
-        <v>159.4780423209646</v>
+        <v>187.5648623917616</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>131.9321652352076</v>
+        <v>158.4688056809989</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>81.09530561389926</v>
+        <v>93.63124204942677</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.534872572365265</v>
+        <v>2.688025214227767</v>
       </c>
       <c r="C2" t="n">
-        <v>4.55236410459246</v>
+        <v>2.970768553050848</v>
       </c>
       <c r="D2" t="n">
-        <v>9.245118130892212</v>
+        <v>12.56048012813369</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.13211933391259</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C3" t="n">
-        <v>37.5665759030042</v>
+        <v>29.14318060056657</v>
       </c>
       <c r="D3" t="n">
-        <v>63.92159302350982</v>
+        <v>83.66944809443441</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.10345302850696</v>
+        <v>44.91201222617884</v>
       </c>
       <c r="C4" t="n">
-        <v>123.4282666210217</v>
+        <v>113.5626839410455</v>
       </c>
       <c r="D4" t="n">
-        <v>127.6399642722406</v>
+        <v>140.211243625121</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>45.3076565509903</v>
       </c>
       <c r="C5" t="n">
-        <v>224.0348261091222</v>
+        <v>220.696883914683</v>
       </c>
       <c r="D5" t="n">
-        <v>102.7398972494287</v>
+        <v>93.95325529641977</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="C6" t="n">
-        <v>203.914888658288</v>
+        <v>226.6570742271654</v>
       </c>
       <c r="D6" t="n">
-        <v>50.31456984264904</v>
+        <v>44.1560664939088</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>168.7005802546591</v>
+        <v>199.3026379437365</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>99.80447161373074</v>
+        <v>115.5762484824558</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.076797305109504</v>
+        <v>3.251548396465436</v>
       </c>
       <c r="C2" t="n">
-        <v>5.367214699117312</v>
+        <v>6.063273821428301</v>
       </c>
       <c r="D2" t="n">
-        <v>15.93965572615121</v>
+        <v>15.50572324087412</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.13854959948582</v>
+        <v>14.78021168743573</v>
       </c>
       <c r="C3" t="n">
-        <v>27.49384445743193</v>
+        <v>20.36635612460008</v>
       </c>
       <c r="D3" t="n">
-        <v>57.82984851865837</v>
+        <v>75.50621593362219</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.22733316569131</v>
+        <v>41.95106115017045</v>
       </c>
       <c r="C4" t="n">
-        <v>109.9253086968111</v>
+        <v>94.86529891366503</v>
       </c>
       <c r="D4" t="n">
-        <v>129.6692367769187</v>
+        <v>147.8178248376253</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.6525120370882</v>
+        <v>54.3151917374548</v>
       </c>
       <c r="C5" t="n">
-        <v>227.3973119961675</v>
+        <v>217.2116795646068</v>
       </c>
       <c r="D5" t="n">
-        <v>120.1659189998096</v>
+        <v>116.3861903384594</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.27682146153116</v>
+        <v>43.91455655866408</v>
       </c>
       <c r="C6" t="n">
-        <v>271.5376705268083</v>
+        <v>281.3993262159676</v>
       </c>
       <c r="D6" t="n">
-        <v>65.52969576306612</v>
+        <v>58.76741757621409</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
-        <v>223.0776220974815</v>
+        <v>253.859339616436</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>151.7094727372596</v>
+        <v>176.0764507566654</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>66.00780689503428</v>
+        <v>72.55311883924776</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
         <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
+        <v>23.27821981539612</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.98900515327081</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.08946221427348</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.157881453934489</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C2" t="n">
-        <v>2.870630287217673</v>
+        <v>3.841578766717769</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87423848286517</v>
+        <v>12.11476667040564</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.33213382367169</v>
+        <v>13.36158625479909</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01493150420873</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="D3" t="n">
-        <v>57.85930094978577</v>
+        <v>71.74121348783568</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.78590655167874</v>
+        <v>37.72660077879643</v>
       </c>
       <c r="C4" t="n">
-        <v>94.61004451056087</v>
+        <v>78.61835615608459</v>
       </c>
       <c r="D4" t="n">
-        <v>129.5416095753666</v>
+        <v>150.7915386337889</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.19938656608268</v>
+        <v>59.07666810305183</v>
       </c>
       <c r="C5" t="n">
-        <v>225.7037972063418</v>
+        <v>209.014086234146</v>
       </c>
       <c r="D5" t="n">
-        <v>131.3087554430109</v>
+        <v>132.8059206919873</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.76362945411734</v>
+        <v>50.636583089642</v>
       </c>
       <c r="C6" t="n">
-        <v>313.1981343565217</v>
+        <v>314.9289555591089</v>
       </c>
       <c r="D6" t="n">
-        <v>78.00770908404307</v>
+        <v>69.35360307110744</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>280.8083140980109</v>
+        <v>308.2962680692174</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>190.8468449670587</v>
+        <v>219.0524565100695</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>74.77186865084555</v>
+        <v>79.32030576462103</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.05363627083508</v>
+        <v>3.01003846122072</v>
       </c>
       <c r="C2" t="n">
-        <v>8.201520321277853</v>
+        <v>8.985936736971055</v>
       </c>
       <c r="D2" t="n">
-        <v>17.7745421853885</v>
+        <v>15.1110606637669</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.48997421987717</v>
+        <v>10.74522862298134</v>
       </c>
       <c r="C3" t="n">
-        <v>18.73665493555038</v>
+        <v>18.94282195344221</v>
       </c>
       <c r="D3" t="n">
-        <v>54.33482669153972</v>
+        <v>66.49377200863647</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.46836007485052</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C4" t="n">
-        <v>80.43066241812419</v>
+        <v>67.75728130400211</v>
       </c>
       <c r="D4" t="n">
-        <v>128.6099310040364</v>
+        <v>149.5535547787336</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.24847395129502</v>
+        <v>57.97220193577417</v>
       </c>
       <c r="C5" t="n">
-        <v>203.7617360164255</v>
+        <v>181.8933059043278</v>
       </c>
       <c r="D5" t="n">
-        <v>143.138815279185</v>
+        <v>149.8883307458818</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.34352355215771</v>
+        <v>60.98125864929064</v>
       </c>
       <c r="C6" t="n">
-        <v>331.9151543379872</v>
+        <v>322.737776798688</v>
       </c>
       <c r="D6" t="n">
-        <v>94.14862308956488</v>
+        <v>86.98382834397167</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.5184292077671</v>
+        <v>30.24273802932299</v>
       </c>
       <c r="C7" t="n">
-        <v>347.8214306421939</v>
+        <v>369.2608370075358</v>
       </c>
       <c r="D7" t="n">
-        <v>51.86180422454201</v>
+        <v>47.07087542781757</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>261.3608738245858</v>
+        <v>289.0657940384309</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>130.7953013936898</v>
+        <v>146.4374875654542</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>52.67076433284138</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>18.87606310955342</v>
+      </c>
+      <c r="D12" t="n">
         <v>19.96089432274615</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.898741117742336</v>
+        <v>5.60479764354504</v>
       </c>
       <c r="C2" t="n">
-        <v>9.787042863636453</v>
+        <v>12.93648949886022</v>
       </c>
       <c r="D2" t="n">
-        <v>8.281041885321844</v>
+        <v>6.883033154474388</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.929535149472482</v>
+        <v>2.202060100625596</v>
       </c>
       <c r="C2" t="n">
-        <v>4.788965301315941</v>
+        <v>5.247441479199201</v>
       </c>
       <c r="D2" t="n">
-        <v>13.22512332390878</v>
+        <v>11.24199296133022</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.59858836215007</v>
+        <v>14.31388152791849</v>
       </c>
       <c r="C3" t="n">
-        <v>25.22109852210056</v>
+        <v>26.50227927614264</v>
       </c>
       <c r="D3" t="n">
-        <v>60.46093236603981</v>
+        <v>72.48243300454202</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.03963942773092</v>
+        <v>44.15901173702154</v>
       </c>
       <c r="C4" t="n">
-        <v>116.0003634906904</v>
+        <v>99.52369177031616</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6812387335479</v>
+        <v>150.7915386337889</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.63744166415923</v>
+        <v>34.87658719336795</v>
       </c>
       <c r="C5" t="n">
-        <v>289.73829121584</v>
+        <v>273.3676482475244</v>
       </c>
       <c r="D5" t="n">
-        <v>131.750541909922</v>
+        <v>134.4258044039945</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.16607959293373</v>
+        <v>18.75727163733956</v>
       </c>
       <c r="C6" t="n">
-        <v>290.8987170022597</v>
+        <v>300.1565978533071</v>
       </c>
       <c r="D6" t="n">
-        <v>74.90833158173589</v>
+        <v>68.70957657712154</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>183.7920059643411</v>
+        <v>203.2551542010341</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>96.38308086443061</v>
+        <v>107.8989814352457</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>15.10418842983717</v>
+      </c>
+      <c r="D11" t="n">
         <v>15.99267010218054</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.787803627162447</v>
+        <v>6.983171420307562</v>
       </c>
       <c r="C2" t="n">
-        <v>4.436517875491336</v>
+        <v>7.645851120674159</v>
       </c>
       <c r="D2" t="n">
-        <v>15.75312366234432</v>
+        <v>11.53357202949153</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65258448588365</v>
+        <v>11.90859965251381</v>
       </c>
       <c r="C3" t="n">
-        <v>24.66150233067988</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D3" t="n">
-        <v>10.09236639965721</v>
+        <v>8.919177893082272</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39771590190257</v>
+        <v>13.39763743294295</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14098325113699</v>
+        <v>70.14057244305428</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576201870812067</v>
+        <v>1.576192639169759</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.695699269412493</v>
+        <v>4.931318718431728</v>
       </c>
       <c r="C2" t="n">
-        <v>4.733005682173872</v>
+        <v>5.980807014271569</v>
       </c>
       <c r="D2" t="n">
-        <v>23.59532432386784</v>
+        <v>10.87874631075891</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96383956585889</v>
+        <v>19.21280257211008</v>
       </c>
       <c r="C3" t="n">
-        <v>20.05710559776234</v>
+        <v>30.85633034447725</v>
       </c>
       <c r="D3" t="n">
-        <v>20.88177366932966</v>
+        <v>16.44918278465531</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.98718052658256</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="C4" t="n">
-        <v>38.1350078237631</v>
+        <v>50.22130381074558</v>
       </c>
       <c r="D4" t="n">
-        <v>20.35653864755761</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43938651321861</v>
+        <v>15.43868861816933</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13552475795646</v>
+        <v>86.13163123820785</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250397160677602</v>
+        <v>3.25025023540407</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.977460860531329</v>
+        <v>6.267477343911637</v>
       </c>
       <c r="C2" t="n">
-        <v>8.138688468206057</v>
+        <v>6.615016031215008</v>
       </c>
       <c r="D2" t="n">
-        <v>26.31378371692726</v>
+        <v>18.85642815546849</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87762569433442</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="C3" t="n">
-        <v>19.06063167795183</v>
+        <v>26.55136666135499</v>
       </c>
       <c r="D3" t="n">
-        <v>34.91094836301658</v>
+        <v>21.33337761328319</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.32873091666921</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C4" t="n">
-        <v>45.26936839052468</v>
+        <v>65.39617807528853</v>
       </c>
       <c r="D4" t="n">
-        <v>26.25291535926396</v>
+        <v>23.55998140651495</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.60349710067131</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43604451606839</v>
+        <v>55.19876467127693</v>
       </c>
       <c r="D5" t="n">
-        <v>29.99239236474006</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.23368131580652</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73006563471311</v>
+        <v>16.72886912011636</v>
       </c>
       <c r="C21" t="n">
-        <v>102.05340037175</v>
+        <v>102.0461016327098</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182516408678278</v>
+        <v>4.182217280029089</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.899321954819084</v>
+        <v>7.16872173641021</v>
       </c>
       <c r="C2" t="n">
-        <v>6.66999390265283</v>
+        <v>9.035024122183396</v>
       </c>
       <c r="D2" t="n">
-        <v>24.62714116103124</v>
+        <v>24.98155208226433</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.38184310368978</v>
+        <v>19.81657741022187</v>
       </c>
       <c r="C3" t="n">
-        <v>26.28138604268712</v>
+        <v>26.02122290106171</v>
       </c>
       <c r="D3" t="n">
-        <v>47.14352475793184</v>
+        <v>30.91523520673206</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.95785126864217</v>
+        <v>31.05169813762236</v>
       </c>
       <c r="C4" t="n">
-        <v>46.62221672697677</v>
+        <v>65.31960175435728</v>
       </c>
       <c r="D4" t="n">
-        <v>37.21609197258809</v>
+        <v>28.65230674844316</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.30516897176729</v>
+        <v>26.43355693684537</v>
       </c>
       <c r="C5" t="n">
-        <v>64.67263001725864</v>
+        <v>90.6153131019806</v>
       </c>
       <c r="D5" t="n">
-        <v>32.32404316232624</v>
+        <v>31.24412068765475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>40.6139207769863</v>
+        <v>51.15985461600555</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05136238131251</v>
+        <v>18.04771215894363</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7636498209435</v>
+        <v>117.7398364654894</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017120793770837</v>
+        <v>6.015904052981208</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.62934133615121</v>
+        <v>6.615016031215008</v>
       </c>
       <c r="C2" t="n">
-        <v>6.405903770210438</v>
+        <v>7.960992133737386</v>
       </c>
       <c r="D2" t="n">
-        <v>19.68207797474005</v>
+        <v>22.96504229774139</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.89096925156637</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="C3" t="n">
-        <v>24.48478774391545</v>
+        <v>29.19717672430014</v>
       </c>
       <c r="D3" t="n">
-        <v>52.09644192585699</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.96838845148163</v>
+        <v>25.24466046700248</v>
       </c>
       <c r="C4" t="n">
-        <v>47.98782778358409</v>
+        <v>54.45852690227482</v>
       </c>
       <c r="D4" t="n">
-        <v>45.07792758819654</v>
+        <v>32.45559735469531</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.56194490192345</v>
+        <v>22.23658550119026</v>
       </c>
       <c r="C5" t="n">
-        <v>56.59775514982863</v>
+        <v>78.36801049150165</v>
       </c>
       <c r="D5" t="n">
-        <v>30.60598467989432</v>
+        <v>27.63619787454772</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20883452356409</v>
+        <v>12.80002656796992</v>
       </c>
       <c r="C6" t="n">
-        <v>48.86551023118075</v>
+        <v>66.85800040691205</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99377502307181</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>25.75124228239384</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053359876585115</v>
+        <v>7.049729029687242</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12524884298546</v>
+        <v>66.0912096533179</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408349922865697</v>
+        <v>4.406080643554526</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.713370728088937</v>
+        <v>4.858669388317464</v>
       </c>
       <c r="C2" t="n">
-        <v>7.694938505886499</v>
+        <v>6.264532100798897</v>
       </c>
       <c r="D2" t="n">
-        <v>15.27010379185489</v>
+        <v>28.09761929554372</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6973850273805</v>
+        <v>21.8831563276614</v>
       </c>
       <c r="C3" t="n">
-        <v>24.8382169174443</v>
+        <v>30.39000018496002</v>
       </c>
       <c r="D3" t="n">
-        <v>56.03815895840794</v>
+        <v>49.98077562320512</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>33.6425303291297</v>
       </c>
       <c r="C4" t="n">
-        <v>56.46227396664256</v>
+        <v>65.56209343730625</v>
       </c>
       <c r="D4" t="n">
-        <v>61.49078570779472</v>
+        <v>46.13723336107885</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.1214022246239</v>
+        <v>31.14594591723007</v>
       </c>
       <c r="C5" t="n">
-        <v>76.30634031258334</v>
+        <v>92.16156573616934</v>
       </c>
       <c r="D5" t="n">
-        <v>40.96342295969817</v>
+        <v>33.20761609614836</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.31200014796801</v>
+        <v>22.74218556887737</v>
       </c>
       <c r="C6" t="n">
-        <v>72.65423885278521</v>
+        <v>100.951152932291</v>
       </c>
       <c r="D6" t="n">
-        <v>34.21390749300134</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>52.4007837141735</v>
+        <v>68.80971484295469</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>28.03871443328891</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.275065729379082</v>
+        <v>7.268185016676278</v>
       </c>
       <c r="C21" t="n">
-        <v>75.47880694230798</v>
+        <v>75.40741954801639</v>
       </c>
       <c r="D21" t="n">
-        <v>5.456299297034311</v>
+        <v>5.451138762507208</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.795436624618169</v>
+        <v>5.852198065015236</v>
       </c>
       <c r="C2" t="n">
-        <v>5.521349088684061</v>
+        <v>6.805475085838889</v>
       </c>
       <c r="D2" t="n">
-        <v>24.96977110981337</v>
+        <v>33.03679199560941</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36220814960484</v>
+        <v>19.02136176978195</v>
       </c>
       <c r="C3" t="n">
-        <v>27.93563092434299</v>
+        <v>26.78207737185298</v>
       </c>
       <c r="D3" t="n">
-        <v>55.25276079501049</v>
+        <v>61.33959656134072</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.5021404074224</v>
+        <v>38.73485567105791</v>
       </c>
       <c r="C4" t="n">
-        <v>59.88268296823845</v>
+        <v>71.68819911180634</v>
       </c>
       <c r="D4" t="n">
-        <v>75.78503228162829</v>
+        <v>59.57637768451344</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.97538385859838</v>
+        <v>41.1843161931537</v>
       </c>
       <c r="C5" t="n">
-        <v>92.35791527701869</v>
+        <v>108.4585776266664</v>
       </c>
       <c r="D5" t="n">
-        <v>53.4070751110265</v>
+        <v>42.31332605303754</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.01264921363075</v>
+        <v>33.20761609614837</v>
       </c>
       <c r="C6" t="n">
-        <v>98.81781517096272</v>
+        <v>125.8266762624967</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>35.94472869558847</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>81.80510920406972</v>
+        <v>109.5326096151124</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>50.90361846519712</v>
+        <v>63.42090169434395</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.484774269054573</v>
+        <v>7.472331528963722</v>
       </c>
       <c r="C21" t="n">
-        <v>84.20371052686396</v>
+        <v>84.06372970084188</v>
       </c>
       <c r="D21" t="n">
-        <v>6.549177485422752</v>
+        <v>6.538290087843257</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_10_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497649741</v>
+        <v>10.84497633145157</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890725175275</v>
+        <v>37.78907193924913</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.855143308127976</v>
+        <v>4.670173829102077</v>
       </c>
       <c r="C2" t="n">
-        <v>12.0970952117292</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="D2" t="n">
-        <v>34.15303913533804</v>
+        <v>32.36036782738336</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3747909433108</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50718801466388</v>
+        <v>33.67885499418683</v>
       </c>
       <c r="D3" t="n">
-        <v>72.07009896875836</v>
+        <v>71.0392638792992</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.34371917414018</v>
+        <v>29.52017171899734</v>
       </c>
       <c r="C4" t="n">
-        <v>69.14841780091984</v>
+        <v>81.43891731038566</v>
       </c>
       <c r="D4" t="n">
-        <v>75.01926907231577</v>
+        <v>79.43517024601793</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.72552122010096</v>
+        <v>40.00621894805753</v>
       </c>
       <c r="C5" t="n">
-        <v>119.5523266846554</v>
+        <v>111.0356653503143</v>
       </c>
       <c r="D5" t="n">
-        <v>52.40078371417351</v>
+        <v>56.57321145722246</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.99505987041232</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>149.4946499164788</v>
+        <v>132.1059345788593</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>42.10323204432872</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.2845522699781</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="C7" t="n">
-        <v>146.0035550801771</v>
+        <v>127.498592602829</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>38.38731698375453</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>102.9755166984479</v>
+        <v>92.12720456652069</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>55.02499532762521</v>
+        <v>50.80937068558941</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660716339345377</v>
+        <v>7.683176150723031</v>
       </c>
       <c r="C21" t="n">
-        <v>92.88618561456269</v>
+        <v>93.15851082751674</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660716339345377</v>
+        <v>8.643573169563409</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.299294181075035</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C2" t="n">
-        <v>11.9272528588945</v>
+        <v>10.08843940884022</v>
       </c>
       <c r="D2" t="n">
-        <v>28.78582443622073</v>
+        <v>30.89952724346411</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.27170743436489</v>
+        <v>14.49550485320416</v>
       </c>
       <c r="C3" t="n">
-        <v>36.45720099720531</v>
+        <v>30.06111470403734</v>
       </c>
       <c r="D3" t="n">
-        <v>79.97316798794517</v>
+        <v>78.60853867904211</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.56519324467246</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="C4" t="n">
-        <v>66.92770449391357</v>
+        <v>81.83456163519713</v>
       </c>
       <c r="D4" t="n">
-        <v>89.2752274856837</v>
+        <v>94.18887474543899</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.79348279587224</v>
+        <v>42.26423866782519</v>
       </c>
       <c r="C5" t="n">
-        <v>123.11116211255</v>
+        <v>129.7134154236099</v>
       </c>
       <c r="D5" t="n">
-        <v>64.91806694332035</v>
+        <v>69.06595099376312</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.89696721544566</v>
+        <v>44.63908636439822</v>
       </c>
       <c r="C6" t="n">
-        <v>166.7223586306019</v>
+        <v>151.587736021933</v>
       </c>
       <c r="D6" t="n">
-        <v>46.41015922285948</v>
+        <v>49.30827844579606</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.34550274309942</v>
+        <v>33.77604801690726</v>
       </c>
       <c r="C7" t="n">
-        <v>178.8813039476985</v>
+        <v>157.8611038520701</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66300816219864</v>
+        <v>41.14210104187108</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.03041848329842</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>143.1977201414398</v>
+        <v>127.1755976081318</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>87.86249253927252</v>
+        <v>80.20780568926014</v>
       </c>
       <c r="D9" t="n">
         <v>35.38905949498476</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>44.69897297435728</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.832510766935026</v>
+        <v>7.861020663159237</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8435761242884</v>
+        <v>101.2106410381752</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811574612801904</v>
+        <v>9.826275828949047</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.728317927830891</v>
+        <v>5.904230693340318</v>
       </c>
       <c r="C2" t="n">
-        <v>10.52433538952581</v>
+        <v>9.546514676095985</v>
       </c>
       <c r="D2" t="n">
-        <v>33.71616140694821</v>
+        <v>40.45193240578558</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.01921834792421</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>40.938879267092</v>
+        <v>34.02737542919444</v>
       </c>
       <c r="D3" t="n">
-        <v>82.52571201898689</v>
+        <v>82.68279165166638</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.60798923303181</v>
+        <v>26.84000048640355</v>
       </c>
       <c r="C4" t="n">
-        <v>76.38488012892309</v>
+        <v>77.75049118553039</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6460503804485</v>
+        <v>106.2879334525767</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.16163818496479</v>
+        <v>41.55247158224626</v>
       </c>
       <c r="C5" t="n">
-        <v>121.6139968635737</v>
+        <v>138.6964069174682</v>
       </c>
       <c r="D5" t="n">
-        <v>76.64995200906974</v>
+        <v>83.08039947188634</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.53849043467533</v>
+        <v>49.63029169278902</v>
       </c>
       <c r="C6" t="n">
-        <v>177.4695507489917</v>
+        <v>173.4041335057056</v>
       </c>
       <c r="D6" t="n">
-        <v>53.85671555957153</v>
+        <v>56.75483478250812</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.1669067763845</v>
+        <v>41.74096714146164</v>
       </c>
       <c r="C7" t="n">
-        <v>205.8901650392326</v>
+        <v>184.9298515535632</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.45872252425729</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="C8" t="n">
-        <v>181.1668126031851</v>
+        <v>161.3060565462722</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>13.53437385074652</v>
       </c>
       <c r="C9" t="n">
-        <v>124.0281144683165</v>
+        <v>112.3796779574281</v>
       </c>
       <c r="D9" t="n">
         <v>36.83124687252333</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>69.89552780385168</v>
+        <v>65.76727870749383</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1531,7 +1531,7 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>41.22554959673205</v>
+        <v>40.51476425885736</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.988025402656631</v>
+        <v>8.022677551276196</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8383429358645</v>
+        <v>109.3089816361382</v>
       </c>
       <c r="D21" t="n">
-        <v>9.98503175332079</v>
+        <v>11.03118163300477</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.157922511663494</v>
+        <v>5.430046552189108</v>
       </c>
       <c r="C2" t="n">
-        <v>7.324819621385452</v>
+        <v>6.567892141411161</v>
       </c>
       <c r="D2" t="n">
-        <v>27.76480682380404</v>
+        <v>33.15460172011903</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.74004214701962</v>
+        <v>18.75628988963531</v>
       </c>
       <c r="C3" t="n">
-        <v>57.46169312956582</v>
+        <v>50.35383975081891</v>
       </c>
       <c r="D3" t="n">
-        <v>87.50808161803945</v>
+        <v>87.96459430051421</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.53820303057228</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="C4" t="n">
-        <v>101.0296927486308</v>
+        <v>111.7759031193164</v>
       </c>
       <c r="D4" t="n">
-        <v>95.20989235785567</v>
+        <v>99.24291192690157</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.09118902997049</v>
+        <v>27.95526587842793</v>
       </c>
       <c r="C5" t="n">
-        <v>106.0287520586555</v>
+        <v>103.5989264906447</v>
       </c>
       <c r="D5" t="n">
-        <v>52.76893910326607</v>
+        <v>56.22959976073608</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.51075515258238</v>
+        <v>25.92206638293279</v>
       </c>
       <c r="C6" t="n">
-        <v>135.6078286399077</v>
+        <v>121.8015106750848</v>
       </c>
       <c r="D6" t="n">
-        <v>28.57867567062465</v>
+        <v>29.66547037922588</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>127.3788193829109</v>
+        <v>113.425239262451</v>
       </c>
       <c r="D7" t="n">
-        <v>27.36818075128833</v>
+        <v>27.78738702100172</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>91.37616757277186</v>
+        <v>82.78096642209104</v>
       </c>
       <c r="D8" t="n">
         <v>27.12078032981814</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>53.36093296892687</v>
+        <v>50.14374574211007</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1828,7 +1828,7 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.384485247166255</v>
+        <v>3.312416754128738</v>
       </c>
       <c r="C2" t="n">
-        <v>4.070325981807276</v>
+        <v>3.414518515370407</v>
       </c>
       <c r="D2" t="n">
-        <v>19.35221074611313</v>
+        <v>22.71960537167969</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.2849121228766</v>
+        <v>19.23243752619501</v>
       </c>
       <c r="C3" t="n">
-        <v>43.88412237983243</v>
+        <v>38.53359739168731</v>
       </c>
       <c r="D3" t="n">
-        <v>90.28642762105792</v>
+        <v>94.32141068551232</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.61249706092554</v>
+        <v>27.04420400888689</v>
       </c>
       <c r="C4" t="n">
-        <v>124.6279623156114</v>
+        <v>122.5604016504676</v>
       </c>
       <c r="D4" t="n">
-        <v>113.1925650565445</v>
+        <v>115.8089226883622</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.74819922828986</v>
+        <v>30.31146036862028</v>
       </c>
       <c r="C5" t="n">
-        <v>143.6296891313084</v>
+        <v>151.3118649170397</v>
       </c>
       <c r="D5" t="n">
-        <v>67.17608666308801</v>
+        <v>72.3793494955961</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.98498035146259</v>
+        <v>30.75226508782709</v>
       </c>
       <c r="C6" t="n">
-        <v>155.0896300829814</v>
+        <v>144.2216829969692</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>157.5017841923158</v>
+        <v>141.2725128934118</v>
       </c>
       <c r="D7" t="n">
-        <v>29.64387192973244</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>117.3286681345363</v>
+        <v>106.3969074477481</v>
       </c>
       <c r="D8" t="n">
         <v>27.87181732356695</v>
@@ -2125,10 +2125,10 @@
         <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>57.35468262980289</v>
+        <v>55.46874528994476</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.414919425997907</v>
+        <v>2.784236489243954</v>
       </c>
       <c r="C2" t="n">
-        <v>6.129050917612838</v>
+        <v>6.083890523217484</v>
       </c>
       <c r="D2" t="n">
-        <v>17.94045754740621</v>
+        <v>23.11917668730814</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.11601046001715</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6242369756475</v>
+        <v>25.46162670964103</v>
       </c>
       <c r="D3" t="n">
-        <v>85.09789100411354</v>
+        <v>90.60058688641691</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.98109441837461</v>
+        <v>31.74088502600363</v>
       </c>
       <c r="C4" t="n">
-        <v>117.0724319837279</v>
+        <v>109.2616472487403</v>
       </c>
       <c r="D4" t="n">
-        <v>129.5798977358322</v>
+        <v>133.4087137823948</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>35.02384934900497</v>
       </c>
       <c r="C5" t="n">
-        <v>183.9549760832461</v>
+        <v>187.0229376590174</v>
       </c>
       <c r="D5" t="n">
-        <v>88.23457491918209</v>
+        <v>93.266031903447</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.38499363544755</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>189.9073124140945</v>
+        <v>190.1085706934651</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55858305264999</v>
+        <v>47.53720558733482</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.84727363096077</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>187.5648623917616</v>
+        <v>172.0542304123663</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>158.4688056809989</v>
+        <v>143.6984114706056</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>93.63124204942677</v>
+        <v>88.52811748275185</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.46605242207675</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.688025214227767</v>
+        <v>1.675843331149305</v>
       </c>
       <c r="C2" t="n">
-        <v>2.970768553050848</v>
+        <v>2.902046213753571</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56048012813369</v>
+        <v>16.12422429454961</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.84602984134927</v>
+        <v>14.40714755982194</v>
       </c>
       <c r="C3" t="n">
-        <v>29.14318060056657</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="D3" t="n">
-        <v>83.66944809443441</v>
+        <v>91.17000055488005</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.91201222617884</v>
+        <v>34.95709050511617</v>
       </c>
       <c r="C4" t="n">
-        <v>113.5626839410455</v>
+        <v>103.8247284626214</v>
       </c>
       <c r="D4" t="n">
-        <v>140.211243625121</v>
+        <v>145.0355518437898</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>36.91371367968008</v>
       </c>
       <c r="C5" t="n">
-        <v>220.696883914683</v>
+        <v>219.7396799030424</v>
       </c>
       <c r="D5" t="n">
-        <v>93.95325529641977</v>
+        <v>99.1319744363217</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C6" t="n">
-        <v>226.6570742271654</v>
+        <v>227.2205974094031</v>
       </c>
       <c r="D6" t="n">
-        <v>44.1560664939088</v>
+        <v>46.93343074922303</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>199.3026379437365</v>
+        <v>183.672232744423</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>115.5762484824558</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.18348900970292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.251548396465436</v>
+        <v>2.482839944040183</v>
       </c>
       <c r="C2" t="n">
-        <v>6.063273821428301</v>
+        <v>10.17483320681394</v>
       </c>
       <c r="D2" t="n">
-        <v>15.50572324087412</v>
+        <v>18.42740440871263</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78021168743573</v>
+        <v>10.16599747747572</v>
       </c>
       <c r="C3" t="n">
-        <v>20.36635612460008</v>
+        <v>18.83973844449629</v>
       </c>
       <c r="D3" t="n">
-        <v>75.50621593362219</v>
+        <v>84.47938995043803</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.95106115017045</v>
+        <v>31.80469862677967</v>
       </c>
       <c r="C4" t="n">
-        <v>94.86529891366503</v>
+        <v>85.38259783834509</v>
       </c>
       <c r="D4" t="n">
-        <v>147.8178248376253</v>
+        <v>154.7479818819035</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.3151917374548</v>
+        <v>43.56505437595222</v>
       </c>
       <c r="C5" t="n">
-        <v>217.2116795646068</v>
+        <v>208.4004939189917</v>
       </c>
       <c r="D5" t="n">
-        <v>116.3861903384594</v>
+        <v>122.0066959452724</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.91455655866408</v>
+        <v>37.27303333943441</v>
       </c>
       <c r="C6" t="n">
-        <v>281.3993262159676</v>
+        <v>282.3653659569464</v>
       </c>
       <c r="D6" t="n">
-        <v>58.76741757621409</v>
+        <v>61.82654342264714</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>253.859339616436</v>
+        <v>247.6910187906533</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>38.20765715387736</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>176.0764507566654</v>
+        <v>161.890196430299</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>72.55311883924776</v>
+        <v>70.11249404649018</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3173,7 +3173,7 @@
         <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.310052348092745</v>
+        <v>1.717076734727671</v>
       </c>
       <c r="C2" t="n">
-        <v>3.841578766717769</v>
+        <v>5.478152189697202</v>
       </c>
       <c r="D2" t="n">
-        <v>12.11476667040564</v>
+        <v>14.19116306488765</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.36158625479909</v>
+        <v>9.52295273119406</v>
       </c>
       <c r="C3" t="n">
-        <v>22.15804568485051</v>
+        <v>28.57376693210342</v>
       </c>
       <c r="D3" t="n">
-        <v>71.74121348783568</v>
+        <v>81.61268665403736</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.72660077879643</v>
+        <v>27.6568145763369</v>
       </c>
       <c r="C4" t="n">
-        <v>78.61835615608459</v>
+        <v>70.90967318233861</v>
       </c>
       <c r="D4" t="n">
-        <v>150.7915386337889</v>
+        <v>159.6233409811931</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.07666810305183</v>
+        <v>46.8784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>209.014086234146</v>
+        <v>196.3495408493621</v>
       </c>
       <c r="D5" t="n">
-        <v>132.8059206919873</v>
+        <v>138.0091835244954</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.636583089642</v>
+        <v>43.23027840880406</v>
       </c>
       <c r="C6" t="n">
-        <v>314.9289555591089</v>
+        <v>311.9905846802982</v>
       </c>
       <c r="D6" t="n">
-        <v>69.35360307110744</v>
+        <v>74.82782826998766</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>14.25301317025519</v>
       </c>
       <c r="C7" t="n">
-        <v>308.2962680692174</v>
+        <v>305.1222777413874</v>
       </c>
       <c r="D7" t="n">
-        <v>40.12402867256714</v>
+        <v>42.22006002113408</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>219.0524565100695</v>
+        <v>205.6172391774519</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3372,7 +3372,7 @@
         <v>79.32030576462103</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3470,7 +3470,7 @@
         <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.01003846122072</v>
+        <v>3.000220984178252</v>
       </c>
       <c r="C2" t="n">
-        <v>8.985936736971055</v>
+        <v>6.026949156371169</v>
       </c>
       <c r="D2" t="n">
-        <v>15.1110606637669</v>
+        <v>14.46899766518949</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.74522862298134</v>
+        <v>7.745989386507334</v>
       </c>
       <c r="C3" t="n">
-        <v>18.94282195344221</v>
+        <v>25.27509464583413</v>
       </c>
       <c r="D3" t="n">
-        <v>66.49377200863647</v>
+        <v>75.10860811340223</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>23.16433708170349</v>
       </c>
       <c r="C4" t="n">
-        <v>67.75728130400211</v>
+        <v>70.82033414125216</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5535547787336</v>
+        <v>162.3290376540974</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.97220193577417</v>
+        <v>45.25856916577796</v>
       </c>
       <c r="C5" t="n">
-        <v>181.8933059043278</v>
+        <v>168.6397118969959</v>
       </c>
       <c r="D5" t="n">
-        <v>149.8883307458818</v>
+        <v>156.5151277495478</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.98125864929064</v>
+        <v>50.4353248102714</v>
       </c>
       <c r="C6" t="n">
-        <v>322.737776798688</v>
+        <v>313.1578827006476</v>
       </c>
       <c r="D6" t="n">
-        <v>86.98382834397167</v>
+        <v>92.73981513397071</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>369.2608370075358</v>
+        <v>362.6733099120397</v>
       </c>
       <c r="D7" t="n">
-        <v>47.07087542781757</v>
+        <v>49.88554609589318</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>289.0657940384309</v>
+        <v>282.8071524238574</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>146.4374875654542</v>
+        <v>140.1140506024005</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>52.67076433284138</v>
+        <v>53.66723825265189</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.60479764354504</v>
+        <v>3.817035074111599</v>
       </c>
       <c r="C2" t="n">
-        <v>12.93648949886022</v>
+        <v>10.47721149972196</v>
       </c>
       <c r="D2" t="n">
-        <v>6.883033154474388</v>
+        <v>6.844744994008762</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.202060100625596</v>
+        <v>2.166717183272711</v>
       </c>
       <c r="C2" t="n">
-        <v>5.247441479199201</v>
+        <v>3.519565519724815</v>
       </c>
       <c r="D2" t="n">
-        <v>11.24199296133022</v>
+        <v>10.76486357706628</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.31388152791849</v>
+        <v>10.75995483854504</v>
       </c>
       <c r="C3" t="n">
-        <v>26.50227927614264</v>
+        <v>28.58849314766712</v>
       </c>
       <c r="D3" t="n">
-        <v>72.48243300454202</v>
+        <v>80.3511408540802</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.15901173702154</v>
+        <v>33.3489877655599</v>
       </c>
       <c r="C4" t="n">
-        <v>99.52369177031616</v>
+        <v>102.2804393238412</v>
       </c>
       <c r="D4" t="n">
-        <v>150.7915386337889</v>
+        <v>164.4604119200172</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.87658719336795</v>
+        <v>29.23153789394879</v>
       </c>
       <c r="C5" t="n">
-        <v>273.3676482475244</v>
+        <v>258.4205394503667</v>
       </c>
       <c r="D5" t="n">
-        <v>134.4258044039945</v>
+        <v>140.9298829446297</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.75727163733956</v>
+        <v>16.14091400552181</v>
       </c>
       <c r="C6" t="n">
-        <v>300.1565978533071</v>
+        <v>297.1779753186223</v>
       </c>
       <c r="D6" t="n">
-        <v>68.70957657712154</v>
+        <v>73.09700706740053</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>203.2551542010341</v>
+        <v>198.8834316740231</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.9794497181356</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8989814352457</v>
+        <v>103.2258623630309</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>40.15937158992001</v>
+        <v>40.93593402397924</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.983171420307562</v>
+        <v>6.219371706403543</v>
       </c>
       <c r="C2" t="n">
-        <v>7.645851120674159</v>
+        <v>6.817256058289851</v>
       </c>
       <c r="D2" t="n">
-        <v>11.53357202949153</v>
+        <v>11.73188506574938</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.90859965251381</v>
+        <v>8.119053514121122</v>
       </c>
       <c r="C3" t="n">
-        <v>32.59893251951534</v>
+        <v>26.39919576719673</v>
       </c>
       <c r="D3" t="n">
-        <v>8.919177893082272</v>
+        <v>8.884816723433634</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39763743294295</v>
+        <v>13.39837305151004</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14057244305428</v>
+        <v>70.14442362261138</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576192639169759</v>
+        <v>1.576279182530593</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.931318718431728</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C2" t="n">
-        <v>5.980807014271569</v>
+        <v>5.095270585040946</v>
       </c>
       <c r="D2" t="n">
-        <v>10.87874631075891</v>
+        <v>16.77806826557799</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.21280257211008</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="C3" t="n">
-        <v>30.85633034447725</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D3" t="n">
-        <v>16.44918278465531</v>
+        <v>16.5915362017711</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.88583952886689</v>
+        <v>9.59756555671682</v>
       </c>
       <c r="C4" t="n">
-        <v>50.22130381074558</v>
+        <v>40.75136545558085</v>
       </c>
       <c r="D4" t="n">
-        <v>19.7439280801076</v>
+        <v>19.73116535995239</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43868861816933</v>
+        <v>15.44165763654213</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13163123820785</v>
+        <v>86.14819523544557</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25025023540407</v>
+        <v>3.250875291903606</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.267477343911637</v>
+        <v>4.62304993929823</v>
       </c>
       <c r="C2" t="n">
-        <v>6.615016031215008</v>
+        <v>6.883033154474388</v>
       </c>
       <c r="D2" t="n">
-        <v>18.85642815546849</v>
+        <v>17.12560695288136</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01016163440774</v>
+        <v>16.63080610994097</v>
       </c>
       <c r="C3" t="n">
-        <v>26.55136666135499</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="D3" t="n">
-        <v>21.33337761328319</v>
+        <v>26.1635763181775</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.12078032981814</v>
+        <v>21.77320058478576</v>
       </c>
       <c r="C4" t="n">
-        <v>65.39617807528853</v>
+        <v>55.86242611934776</v>
       </c>
       <c r="D4" t="n">
-        <v>23.55998140651495</v>
+        <v>23.623795007291</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.22275891787279</v>
+        <v>8.909360416039807</v>
       </c>
       <c r="C5" t="n">
-        <v>55.19876467127693</v>
+        <v>45.20948178056562</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72886912011636</v>
+        <v>16.73500183288969</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0461016327098</v>
+        <v>102.0835111806271</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182217280029089</v>
+        <v>5.020500549866905</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.16872173641021</v>
+        <v>5.072690387843269</v>
       </c>
       <c r="C2" t="n">
-        <v>9.035024122183396</v>
+        <v>6.971390447856601</v>
       </c>
       <c r="D2" t="n">
-        <v>24.98155208226433</v>
+        <v>23.72295152541993</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.81657741022187</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C3" t="n">
-        <v>26.02122290106171</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>30.91523520673206</v>
+        <v>33.35978699030662</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.05169813762236</v>
+        <v>27.5164246546296</v>
       </c>
       <c r="C4" t="n">
-        <v>65.31960175435728</v>
+        <v>56.05386692167588</v>
       </c>
       <c r="D4" t="n">
-        <v>28.65230674844316</v>
+        <v>31.00064725700153</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.43355693684537</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="C5" t="n">
-        <v>90.6153131019806</v>
+        <v>76.08544707912782</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>31.09685853201772</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.14970867713103</v>
+        <v>9.096874227550947</v>
       </c>
       <c r="C6" t="n">
-        <v>51.15985461600555</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="D6" t="n">
         <v>38.15856976866503</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04771215894363</v>
+        <v>18.0603779398896</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7398364654894</v>
+        <v>117.8224656078512</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015904052981208</v>
+        <v>6.880143977100799</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.615016031215008</v>
+        <v>5.119814277647116</v>
       </c>
       <c r="C2" t="n">
-        <v>7.960992133737386</v>
+        <v>8.712029127486195</v>
       </c>
       <c r="D2" t="n">
-        <v>22.96504229774139</v>
+        <v>25.89163220410113</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.87548227247668</v>
+        <v>15.0060136594125</v>
       </c>
       <c r="C3" t="n">
-        <v>29.19717672430014</v>
+        <v>24.5633275602552</v>
       </c>
       <c r="D3" t="n">
-        <v>40.47254910757476</v>
+        <v>41.36103077991812</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.24466046700248</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="C4" t="n">
-        <v>54.45852690227482</v>
+        <v>49.83842220608933</v>
       </c>
       <c r="D4" t="n">
-        <v>32.45559735469531</v>
+        <v>35.08471770666826</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.23658550119026</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C5" t="n">
-        <v>78.36801049150165</v>
+        <v>66.95519342963247</v>
       </c>
       <c r="D5" t="n">
-        <v>27.63619787454772</v>
+        <v>28.1516154192773</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.80002656796992</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C6" t="n">
-        <v>66.85800040691205</v>
+        <v>56.87558975013048</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>30.06307819944583</v>
+        <v>27.008861091534</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049729029687242</v>
+        <v>7.058079324218395</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0912096533179</v>
+        <v>66.16949366454746</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406080643554526</v>
+        <v>5.293559493163796</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.858669388317464</v>
+        <v>3.975096454495335</v>
       </c>
       <c r="C2" t="n">
-        <v>6.264532100798897</v>
+        <v>10.52335364182156</v>
       </c>
       <c r="D2" t="n">
-        <v>28.09761929554372</v>
+        <v>29.75480942031233</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8831563276614</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="C3" t="n">
-        <v>30.39000018496002</v>
+        <v>30.67470701919159</v>
       </c>
       <c r="D3" t="n">
-        <v>49.98077562320512</v>
+        <v>53.11255079975245</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.6425303291297</v>
+        <v>26.57198336314417</v>
       </c>
       <c r="C4" t="n">
-        <v>65.56209343730625</v>
+        <v>57.27908805657591</v>
       </c>
       <c r="D4" t="n">
-        <v>46.13723336107885</v>
+        <v>48.28137034715389</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.14594591723007</v>
+        <v>26.92443078896878</v>
       </c>
       <c r="C5" t="n">
-        <v>92.16156573616934</v>
+        <v>81.82867114897165</v>
       </c>
       <c r="D5" t="n">
-        <v>33.20761609614836</v>
+        <v>35.22019888985433</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.74218556887737</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>100.951152932291</v>
+        <v>86.62156344110458</v>
       </c>
       <c r="D6" t="n">
-        <v>33.04660947265189</v>
+        <v>33.20761609614837</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.95924962250714</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>68.80971484295469</v>
+        <v>59.70695012917827</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268185016676278</v>
+        <v>7.280406184080118</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40741954801639</v>
+        <v>75.53421415983122</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451138762507208</v>
+        <v>6.370355411070102</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.852198065015236</v>
+        <v>3.624612524079224</v>
       </c>
       <c r="C2" t="n">
-        <v>6.805475085838889</v>
+        <v>8.047385931711105</v>
       </c>
       <c r="D2" t="n">
-        <v>33.03679199560941</v>
+        <v>28.04853191033137</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.02136176978195</v>
+        <v>15.11400590687965</v>
       </c>
       <c r="C3" t="n">
-        <v>26.78207737185298</v>
+        <v>36.9038962026376</v>
       </c>
       <c r="D3" t="n">
-        <v>61.33959656134072</v>
+        <v>64.5940902009189</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.73485567105791</v>
+        <v>30.29869764846506</v>
       </c>
       <c r="C4" t="n">
-        <v>71.68819911180634</v>
+        <v>68.81658707688442</v>
       </c>
       <c r="D4" t="n">
-        <v>59.57637768451344</v>
+        <v>64.05609245899163</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.1843161931537</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>108.4585776266664</v>
+        <v>95.62222639363934</v>
       </c>
       <c r="D5" t="n">
-        <v>42.31332605303754</v>
+        <v>44.30136515413732</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.20761609614837</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="C6" t="n">
-        <v>125.8266762624967</v>
+        <v>110.732305309702</v>
       </c>
       <c r="D6" t="n">
-        <v>35.94472869558847</v>
+        <v>37.19253002768617</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>16.22927129890402</v>
       </c>
       <c r="C7" t="n">
-        <v>109.5326096151124</v>
+        <v>94.98016339506191</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>63.42090169434395</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.472331528963722</v>
+        <v>7.489243886511911</v>
       </c>
       <c r="C21" t="n">
-        <v>84.06372970084188</v>
+        <v>84.253993723259</v>
       </c>
       <c r="D21" t="n">
-        <v>6.538290087843257</v>
+        <v>7.489243886511911</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_10_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_10_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633145157</v>
+        <v>10.84497632217236</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907193924913</v>
+        <v>37.78907190691594</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.670173829102077</v>
+        <v>1.152571804785755</v>
       </c>
       <c r="C2" t="n">
-        <v>6.926230053461247</v>
+        <v>1.484402528821177</v>
       </c>
       <c r="D2" t="n">
-        <v>32.36036782738336</v>
+        <v>14.58288039888212</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.60211444233956</v>
+        <v>11.56007921750619</v>
       </c>
       <c r="C3" t="n">
-        <v>33.67885499418683</v>
+        <v>19.00172681569702</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0392638792992</v>
+        <v>75.34913630094269</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.52017171899734</v>
+        <v>22.75593003673682</v>
       </c>
       <c r="C4" t="n">
-        <v>81.43891731038566</v>
+        <v>77.3293214204085</v>
       </c>
       <c r="D4" t="n">
-        <v>79.43517024601793</v>
+        <v>88.87958316087224</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.00621894805753</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="C5" t="n">
-        <v>111.0356653503143</v>
+        <v>121.7121716339983</v>
       </c>
       <c r="D5" t="n">
-        <v>56.57321145722246</v>
+        <v>51.36994862471437</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C6" t="n">
-        <v>132.1059345788593</v>
+        <v>89.5599343199153</v>
       </c>
       <c r="D6" t="n">
-        <v>42.10323204432872</v>
+        <v>30.22899356146354</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>127.498592602829</v>
+        <v>47.4301950875719</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>92.12720456652069</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>50.80937068558941</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.683176150723031</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.15851082751674</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.643573169563409</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.424156065963627</v>
+        <v>1.256637061435917</v>
       </c>
       <c r="C2" t="n">
-        <v>10.08843940884022</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="D2" t="n">
-        <v>30.89952724346411</v>
+        <v>12.23257639491526</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.49550485320416</v>
+        <v>7.480917506360695</v>
       </c>
       <c r="C3" t="n">
-        <v>30.06111470403734</v>
+        <v>11.22628499806228</v>
       </c>
       <c r="D3" t="n">
-        <v>78.60853867904211</v>
+        <v>69.6697258318749</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.43984833369835</v>
+        <v>22.81974363751286</v>
       </c>
       <c r="C4" t="n">
-        <v>81.83456163519713</v>
+        <v>61.1717177039145</v>
       </c>
       <c r="D4" t="n">
-        <v>94.18887474543899</v>
+        <v>105.6880856052819</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.26423866782519</v>
+        <v>28.78975142703772</v>
       </c>
       <c r="C5" t="n">
-        <v>129.7134154236099</v>
+        <v>134.3276296335698</v>
       </c>
       <c r="D5" t="n">
-        <v>69.06595099376312</v>
+        <v>70.46494147231483</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.63908636439822</v>
+        <v>22.90319219237384</v>
       </c>
       <c r="C6" t="n">
-        <v>151.587736021933</v>
+        <v>142.450610138508</v>
       </c>
       <c r="D6" t="n">
-        <v>49.30827844579606</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.77604801690726</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>157.8611038520701</v>
+        <v>89.05138900911543</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.19316761802514</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>127.1755976081318</v>
+        <v>46.64774216728719</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>80.20780568926014</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69897297435728</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.861020663159237</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2106410381752</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.826275828949047</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.904230693340318</v>
+        <v>0.6715154297048183</v>
       </c>
       <c r="C2" t="n">
-        <v>9.546514676095985</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="D2" t="n">
-        <v>40.45193240578558</v>
+        <v>8.252571201898688</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80613803837365</v>
+        <v>6.867325191206439</v>
       </c>
       <c r="C3" t="n">
-        <v>34.02737542919444</v>
+        <v>18.09361018926871</v>
       </c>
       <c r="D3" t="n">
-        <v>82.68279165166638</v>
+        <v>66.6852128109646</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.84000048640355</v>
+        <v>24.65757533986289</v>
       </c>
       <c r="C4" t="n">
-        <v>77.75049118553039</v>
+        <v>53.76934001389356</v>
       </c>
       <c r="D4" t="n">
-        <v>106.2879334525767</v>
+        <v>117.2511100659008</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.55247158224626</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C5" t="n">
-        <v>138.6964069174682</v>
+        <v>146.3785827031994</v>
       </c>
       <c r="D5" t="n">
-        <v>83.08039947188634</v>
+        <v>79.47247665877931</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.63029169278902</v>
+        <v>17.50947030524187</v>
       </c>
       <c r="C6" t="n">
-        <v>173.4041335057056</v>
+        <v>178.6771004252153</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.74096714146164</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>184.9298515535632</v>
+        <v>84.67966648210437</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>161.3060565462722</v>
+        <v>41.8911745402114</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>112.3796779574281</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>65.76727870749383</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>40.51476425885736</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.022677551276196</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3089816361382</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03118163300477</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.430046552189108</v>
+        <v>0.7156940763959247</v>
       </c>
       <c r="C2" t="n">
-        <v>6.567892141411161</v>
+        <v>2.672317250959818</v>
       </c>
       <c r="D2" t="n">
-        <v>33.15460172011903</v>
+        <v>12.15894531709675</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75628988963531</v>
+        <v>4.511130701014094</v>
       </c>
       <c r="C3" t="n">
-        <v>50.35383975081891</v>
+        <v>13.38612994740526</v>
       </c>
       <c r="D3" t="n">
-        <v>87.96459430051421</v>
+        <v>58.12437282993241</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.96089432274615</v>
+        <v>19.08026663203676</v>
       </c>
       <c r="C4" t="n">
-        <v>111.7759031193164</v>
+        <v>49.60869324329558</v>
       </c>
       <c r="D4" t="n">
-        <v>99.24291192690157</v>
+        <v>125.0491320807332</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.95526587842793</v>
+        <v>33.82120841130262</v>
       </c>
       <c r="C5" t="n">
-        <v>103.5989264906447</v>
+        <v>123.2829679607932</v>
       </c>
       <c r="D5" t="n">
-        <v>56.22959976073608</v>
+        <v>100.8745766113598</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.92206638293279</v>
+        <v>27.04911274740813</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8015106750848</v>
+        <v>207.4570343752105</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>52.60891422747383</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>113.425239262451</v>
+        <v>167.9220543251914</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>74.35266238113219</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>50.14374574211007</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>24.00864010735575</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.91689560250429</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.312416754128738</v>
+        <v>0.4486587008407923</v>
       </c>
       <c r="C2" t="n">
-        <v>3.414518515370407</v>
+        <v>2.509347132054847</v>
       </c>
       <c r="D2" t="n">
-        <v>22.71960537167969</v>
+        <v>9.809623060834129</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.23243752619501</v>
+        <v>3.632466505713198</v>
       </c>
       <c r="C3" t="n">
-        <v>38.53359739168731</v>
+        <v>12.10985793188441</v>
       </c>
       <c r="D3" t="n">
-        <v>94.32141068551232</v>
+        <v>55.13495107050088</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.04420400888689</v>
+        <v>15.28973874593983</v>
       </c>
       <c r="C4" t="n">
-        <v>122.5604016504676</v>
+        <v>43.03589236336318</v>
       </c>
       <c r="D4" t="n">
-        <v>115.8089226883622</v>
+        <v>126.4530312978062</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.31146036862028</v>
+        <v>34.36116964863837</v>
       </c>
       <c r="C5" t="n">
-        <v>151.3118649170397</v>
+        <v>113.6618404591745</v>
       </c>
       <c r="D5" t="n">
-        <v>72.3793494955961</v>
+        <v>118.49694790259</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.75226508782709</v>
+        <v>33.12711278440013</v>
       </c>
       <c r="C6" t="n">
-        <v>144.2216829969692</v>
+        <v>214.018054282692</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>65.40894079544375</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>11.79766216193392</v>
       </c>
       <c r="C7" t="n">
-        <v>141.2725128934118</v>
+        <v>223.7363748070311</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54217107911827</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>106.3969074477481</v>
+        <v>113.6569317206532</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>55.46874528994476</v>
+        <v>50.14374574211007</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.784236489243954</v>
+        <v>1.623810702824224</v>
       </c>
       <c r="C2" t="n">
-        <v>6.083890523217484</v>
+        <v>6.014186436215961</v>
       </c>
       <c r="D2" t="n">
-        <v>23.11917668730814</v>
+        <v>11.34900346109313</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.23181563138926</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C3" t="n">
-        <v>25.46162670964103</v>
+        <v>10.9121257327033</v>
       </c>
       <c r="D3" t="n">
-        <v>90.60058688641691</v>
+        <v>50.99197575857934</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.74088502600363</v>
+        <v>11.32053277766997</v>
       </c>
       <c r="C4" t="n">
-        <v>109.2616472487403</v>
+        <v>36.475854203586</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4087137823948</v>
+        <v>125.3554373644582</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.02384934900497</v>
+        <v>30.06602344255857</v>
       </c>
       <c r="C5" t="n">
-        <v>187.0229376590174</v>
+        <v>96.75123625352319</v>
       </c>
       <c r="D5" t="n">
-        <v>93.266031903447</v>
+        <v>132.904095462412</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1085706934651</v>
+        <v>201.540040961715</v>
       </c>
       <c r="D6" t="n">
-        <v>47.53720558733482</v>
+        <v>84.32721905627979</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="C7" t="n">
-        <v>172.0542304123663</v>
+        <v>264.4592695791888</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>48.86747372658923</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>143.6984114706056</v>
+        <v>196.1875524781613</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>88.52811748275185</v>
+        <v>89.1937424262312</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>46.54956739686252</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.675843331149305</v>
+        <v>1.077958979262998</v>
       </c>
       <c r="C2" t="n">
-        <v>2.902046213753571</v>
+        <v>3.079742548222244</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12422429454961</v>
+        <v>8.171086142446203</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.40714755982194</v>
+        <v>4.471860792844221</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35010838198439</v>
+        <v>17.24930716361646</v>
       </c>
       <c r="D3" t="n">
-        <v>91.17000055488005</v>
+        <v>55.31657439578653</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.95709050511617</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C4" t="n">
-        <v>103.8247284626214</v>
+        <v>52.46754255806228</v>
       </c>
       <c r="D4" t="n">
-        <v>145.0355518437898</v>
+        <v>130.1925083032823</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.91371367968008</v>
+        <v>24.32279937271473</v>
       </c>
       <c r="C5" t="n">
-        <v>219.7396799030424</v>
+        <v>157.8404871502809</v>
       </c>
       <c r="D5" t="n">
-        <v>99.1319744363217</v>
+        <v>123.7002107350981</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.18245050873644</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>227.2205974094031</v>
+        <v>225.5300278626901</v>
       </c>
       <c r="D6" t="n">
-        <v>46.93343074922303</v>
+        <v>70.3196428120863</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>183.672232744423</v>
+        <v>137.9188627357046</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>65.67401267559038</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>35.49999698556465</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.482839944040183</v>
+        <v>0.5723589115758905</v>
       </c>
       <c r="C2" t="n">
-        <v>10.17483320681394</v>
+        <v>1.71118624850219</v>
       </c>
       <c r="D2" t="n">
-        <v>18.42740440871263</v>
+        <v>6.274349577841365</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.16599747747572</v>
+        <v>4.074252972624263</v>
       </c>
       <c r="C3" t="n">
-        <v>18.83973844449629</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="D3" t="n">
-        <v>84.47938995043803</v>
+        <v>49.59298528002763</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.80469862677967</v>
+        <v>13.34980528234813</v>
       </c>
       <c r="C4" t="n">
-        <v>85.38259783834509</v>
+        <v>45.58843639440489</v>
       </c>
       <c r="D4" t="n">
-        <v>154.7479818819035</v>
+        <v>123.3644530202457</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.56505437595222</v>
+        <v>21.96660488252239</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4004939189917</v>
+        <v>115.6498795602743</v>
       </c>
       <c r="D5" t="n">
-        <v>122.0066959452724</v>
+        <v>126.6945412330509</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>14.28933783531233</v>
       </c>
       <c r="C6" t="n">
-        <v>282.3653659569464</v>
+        <v>200.4934979089879</v>
       </c>
       <c r="D6" t="n">
-        <v>61.82654342264714</v>
+        <v>75.91462297858888</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>247.6910187906533</v>
+        <v>164.3887443376071</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20765715387736</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>161.890196430299</v>
+        <v>75.68783925890784</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>70.11249404649018</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.29999819133879</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>18.50594422505238</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.717076734727671</v>
+        <v>0.5988660995905544</v>
       </c>
       <c r="C2" t="n">
-        <v>5.478152189697202</v>
+        <v>8.33798325216816</v>
       </c>
       <c r="D2" t="n">
-        <v>14.19116306488765</v>
+        <v>6.221335201812037</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.52295273119406</v>
+        <v>2.910881943091793</v>
       </c>
       <c r="C3" t="n">
-        <v>28.57376693210342</v>
+        <v>9.616218763097507</v>
       </c>
       <c r="D3" t="n">
-        <v>81.61268665403736</v>
+        <v>43.10363295495621</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6568145763369</v>
+        <v>10.43990508696058</v>
       </c>
       <c r="C4" t="n">
-        <v>70.90967318233861</v>
+        <v>39.87073776487146</v>
       </c>
       <c r="D4" t="n">
-        <v>159.6233409811931</v>
+        <v>120.6842817876519</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.8784528777852</v>
+        <v>21.622993186036</v>
       </c>
       <c r="C5" t="n">
-        <v>196.3495408493621</v>
+        <v>98.76381904722915</v>
       </c>
       <c r="D5" t="n">
-        <v>138.0091835244954</v>
+        <v>142.991553123548</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.23027840880406</v>
+        <v>22.42017232188442</v>
       </c>
       <c r="C6" t="n">
-        <v>311.9905846802982</v>
+        <v>194.4154978719959</v>
       </c>
       <c r="D6" t="n">
-        <v>74.82782826998766</v>
+        <v>97.65051715061327</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.25301317025519</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>305.1222777413874</v>
+        <v>232.5397064710122</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>48.80758711663017</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C8" t="n">
-        <v>205.6172391774519</v>
+        <v>151.5425756275376</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>79.32030576462103</v>
+        <v>64.5656195174957</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>23.18593553119691</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.000220984178252</v>
+        <v>0.8276133146800612</v>
       </c>
       <c r="C2" t="n">
-        <v>6.026949156371169</v>
+        <v>8.919177893082272</v>
       </c>
       <c r="D2" t="n">
-        <v>14.46899766518949</v>
+        <v>13.56088103876119</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.745989386507334</v>
+        <v>2.439643045053324</v>
       </c>
       <c r="C3" t="n">
-        <v>25.27509464583413</v>
+        <v>22.73727683035613</v>
       </c>
       <c r="D3" t="n">
-        <v>75.10860811340223</v>
+        <v>38.2439818189345</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.16433708170349</v>
+        <v>7.938411936539708</v>
       </c>
       <c r="C4" t="n">
-        <v>70.82033414125216</v>
+        <v>31.03893541746715</v>
       </c>
       <c r="D4" t="n">
-        <v>162.3290376540974</v>
+        <v>115.4388038038612</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.25856916577796</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C5" t="n">
-        <v>168.6397118969959</v>
+        <v>85.24024442122932</v>
       </c>
       <c r="D5" t="n">
-        <v>156.5151277495478</v>
+        <v>154.0362147963246</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.4353248102714</v>
+        <v>26.28433128579986</v>
       </c>
       <c r="C6" t="n">
-        <v>313.1578827006476</v>
+        <v>176.1009944492716</v>
       </c>
       <c r="D6" t="n">
-        <v>92.73981513397071</v>
+        <v>117.6958417759246</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>362.6733099120397</v>
+        <v>260.2073202720958</v>
       </c>
       <c r="D7" t="n">
-        <v>49.88554609589318</v>
+        <v>64.37810570598458</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>282.8071524238574</v>
+        <v>232.5711223975482</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>140.1140506024005</v>
+        <v>126.2468642799143</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>25.18281036163492</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>53.66723825265189</v>
+        <v>51.81664383014665</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.817035074111599</v>
+        <v>6.952737241475911</v>
       </c>
       <c r="C2" t="n">
-        <v>10.47721149972196</v>
+        <v>12.94925221901543</v>
       </c>
       <c r="D2" t="n">
-        <v>6.844744994008762</v>
+        <v>16.01623204708246</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.166717183272711</v>
+        <v>0.9611310024576274</v>
       </c>
       <c r="C2" t="n">
-        <v>3.519565519724815</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="D2" t="n">
-        <v>10.76486357706628</v>
+        <v>17.38969708532375</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.75995483854504</v>
+        <v>2.59181393921158</v>
       </c>
       <c r="C3" t="n">
-        <v>28.58849314766712</v>
+        <v>28.8879261974624</v>
       </c>
       <c r="D3" t="n">
-        <v>80.3511408540802</v>
+        <v>39.69205968269855</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3489877655599</v>
+        <v>6.253732876052182</v>
       </c>
       <c r="C4" t="n">
-        <v>102.2804393238412</v>
+        <v>44.13348629671111</v>
       </c>
       <c r="D4" t="n">
-        <v>164.4604119200172</v>
+        <v>108.202341475858</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.23153789394879</v>
+        <v>15.97794388661684</v>
       </c>
       <c r="C5" t="n">
-        <v>258.4205394503667</v>
+        <v>71.44668917656163</v>
       </c>
       <c r="D5" t="n">
-        <v>140.9298829446297</v>
+        <v>160.442118566535</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.14091400552181</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="C6" t="n">
-        <v>297.1779753186223</v>
+        <v>156.2569281033309</v>
       </c>
       <c r="D6" t="n">
-        <v>73.09700706740053</v>
+        <v>136.8153783161313</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>198.8834316740231</v>
+        <v>260.8660729816455</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>79.34975819574845</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>103.2258623630309</v>
+        <v>288.481654154404</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>43.39324852770901</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.993749660876023</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>200.2421704967006</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>95.94620313604078</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>39.80397892098267</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.219371706403543</v>
+        <v>6.554147673551706</v>
       </c>
       <c r="C2" t="n">
-        <v>6.817256058289851</v>
+        <v>10.08058542720625</v>
       </c>
       <c r="D2" t="n">
-        <v>11.73188506574938</v>
+        <v>19.36791870938108</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.119053514121122</v>
+        <v>11.19683256693487</v>
       </c>
       <c r="C3" t="n">
-        <v>26.39919576719673</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="D3" t="n">
-        <v>8.884816723433634</v>
+        <v>13.91627370769854</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39837305151004</v>
+        <v>11.67667688626099</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14442362261138</v>
+        <v>59.94027468280644</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576279182530593</v>
+        <v>0.778445125750733</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.923464736797754</v>
+        <v>4.014366362665207</v>
       </c>
       <c r="C2" t="n">
-        <v>5.095270585040946</v>
+        <v>6.097634991076939</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77806826557799</v>
+        <v>26.44435616159208</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.07611865704152</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51700549170635</v>
+        <v>34.64096774434871</v>
       </c>
       <c r="D3" t="n">
-        <v>16.5915362017711</v>
+        <v>27.45948328778329</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9.59756555671682</v>
+        <v>13.7582123273148</v>
       </c>
       <c r="C4" t="n">
-        <v>40.75136545558085</v>
+        <v>41.45331506411732</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73116535995239</v>
+        <v>21.63281066307847</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44165763654213</v>
+        <v>13.62404560476276</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14819523544557</v>
+        <v>73.73012915518669</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250875291903606</v>
+        <v>1.602828894677971</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.62304993929823</v>
+        <v>2.268818944514379</v>
       </c>
       <c r="C2" t="n">
-        <v>6.883033154474388</v>
+        <v>4.408047192068178</v>
       </c>
       <c r="D2" t="n">
-        <v>17.12560695288136</v>
+        <v>28.36956340962008</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.63080610994097</v>
+        <v>15.9288565014045</v>
       </c>
       <c r="C3" t="n">
-        <v>22.45747873464579</v>
+        <v>27.84727363096077</v>
       </c>
       <c r="D3" t="n">
-        <v>26.1635763181775</v>
+        <v>43.03491061565893</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.77320058478576</v>
+        <v>26.92933952749001</v>
       </c>
       <c r="C4" t="n">
-        <v>55.86242611934776</v>
+        <v>69.04631603967817</v>
       </c>
       <c r="D4" t="n">
-        <v>23.623795007291</v>
+        <v>31.00064725700153</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8.909360416039807</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="C5" t="n">
-        <v>45.20948178056562</v>
+        <v>47.24660826687776</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>27.9798095710341</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73500183288969</v>
+        <v>14.82695864858963</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0835111806271</v>
+        <v>87.31431204169452</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020500549866905</v>
+        <v>2.471159774764939</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.072690387843269</v>
+        <v>3.267256359733385</v>
       </c>
       <c r="C2" t="n">
-        <v>6.971390447856601</v>
+        <v>3.32125248346696</v>
       </c>
       <c r="D2" t="n">
-        <v>23.72295152541993</v>
+        <v>25.22306201750905</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.19883712007237</v>
+        <v>11.41281706186917</v>
       </c>
       <c r="C3" t="n">
-        <v>24.90203051822035</v>
+        <v>21.45118733779281</v>
       </c>
       <c r="D3" t="n">
-        <v>33.35978699030662</v>
+        <v>55.74363464713389</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.5164246546296</v>
+        <v>29.08623923372025</v>
       </c>
       <c r="C4" t="n">
-        <v>56.05386692167588</v>
+        <v>69.46748580480005</v>
       </c>
       <c r="D4" t="n">
-        <v>31.00064725700153</v>
+        <v>45.58843639440489</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.64124548178919</v>
+        <v>26.94897448157495</v>
       </c>
       <c r="C5" t="n">
-        <v>76.08544707912782</v>
+        <v>92.23519681398784</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09685853201772</v>
+        <v>32.88854809226815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.096874227550947</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="C6" t="n">
-        <v>43.51203999992289</v>
+        <v>45.16235789076178</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.2881194078966</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.31256528951153</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0603779398896</v>
+        <v>16.05760501500321</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8224656078512</v>
+        <v>100.5713156202833</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880143977100799</v>
+        <v>3.380548424211203</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.119814277647116</v>
+        <v>2.333614292994668</v>
       </c>
       <c r="C2" t="n">
-        <v>8.712029127486195</v>
+        <v>3.280019079888593</v>
       </c>
       <c r="D2" t="n">
-        <v>25.89163220410113</v>
+        <v>25.74731529157685</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.0060136594125</v>
+        <v>11.26064616771092</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5633275602552</v>
+        <v>16.57190124768616</v>
       </c>
       <c r="D3" t="n">
-        <v>41.36103077991812</v>
+        <v>62.51278506791565</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.45413258090555</v>
+        <v>25.49991487010665</v>
       </c>
       <c r="C4" t="n">
-        <v>49.83842220608933</v>
+        <v>60.78883609925825</v>
       </c>
       <c r="D4" t="n">
-        <v>35.08471770666826</v>
+        <v>62.32036251788328</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.11953654020664</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>66.95519342963247</v>
+        <v>111.3547333541945</v>
       </c>
       <c r="D5" t="n">
-        <v>28.1516154192773</v>
+        <v>41.33157834879072</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.06291396852981</v>
+        <v>22.98369550412208</v>
       </c>
       <c r="C6" t="n">
-        <v>56.87558975013048</v>
+        <v>96.60397409788615</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>27.008861091534</v>
+        <v>41.20198765183014</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.162496759482</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058079324218395</v>
+        <v>17.310887812126</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16949366454746</v>
+        <v>113.3863151694253</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293559493163796</v>
+        <v>4.327721953031499</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.975096454495335</v>
+        <v>2.490693925674158</v>
       </c>
       <c r="C2" t="n">
-        <v>10.52335364182156</v>
+        <v>5.41433858892116</v>
       </c>
       <c r="D2" t="n">
-        <v>29.75480942031233</v>
+        <v>27.25135277448296</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.86151682043897</v>
+        <v>9.478774084502955</v>
       </c>
       <c r="C3" t="n">
-        <v>30.67470701919159</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="D3" t="n">
-        <v>53.11255079975245</v>
+        <v>67.31353134168255</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.57198336314417</v>
+        <v>23.53445596620454</v>
       </c>
       <c r="C4" t="n">
-        <v>57.27908805657591</v>
+        <v>50.27235469136642</v>
       </c>
       <c r="D4" t="n">
-        <v>48.28137034715389</v>
+        <v>76.18067660643975</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.92443078896878</v>
+        <v>36.74190783143688</v>
       </c>
       <c r="C5" t="n">
-        <v>81.82867114897165</v>
+        <v>111.6983450506809</v>
       </c>
       <c r="D5" t="n">
-        <v>35.22019888985433</v>
+        <v>52.86711387369075</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.99878157258428</v>
+        <v>34.61642405174254</v>
       </c>
       <c r="C6" t="n">
-        <v>86.62156344110458</v>
+        <v>135.2455637370406</v>
       </c>
       <c r="D6" t="n">
-        <v>33.20761609614837</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="C7" t="n">
-        <v>59.70695012917827</v>
+        <v>86.95535766054849</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>29.04009709162065</v>
+        <v>39.22082078466007</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280406184080118</v>
+        <v>17.696485599379</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53421415983122</v>
+        <v>126.5298720355598</v>
       </c>
       <c r="D21" t="n">
-        <v>6.370355411070102</v>
+        <v>5.308945679813699</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.624612524079224</v>
+        <v>2.314961086613979</v>
       </c>
       <c r="C2" t="n">
-        <v>8.047385931711105</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="D2" t="n">
-        <v>28.04853191033137</v>
+        <v>21.622993186036</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.11400590687965</v>
+        <v>14.17152811080271</v>
       </c>
       <c r="C3" t="n">
-        <v>36.9038962026376</v>
+        <v>25.13274122871834</v>
       </c>
       <c r="D3" t="n">
-        <v>64.5940902009189</v>
+        <v>73.94523708386976</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.29869764846506</v>
+        <v>17.65084197465341</v>
       </c>
       <c r="C4" t="n">
-        <v>68.81658707688442</v>
+        <v>86.64610713371074</v>
       </c>
       <c r="D4" t="n">
-        <v>64.05609245899163</v>
+        <v>69.65892660712818</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="C5" t="n">
-        <v>95.62222639363934</v>
+        <v>80.79783605951251</v>
       </c>
       <c r="D5" t="n">
-        <v>44.30136515413732</v>
+        <v>39.07355862902306</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.57867567062465</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>110.732305309702</v>
+        <v>57.23785465299754</v>
       </c>
       <c r="D6" t="n">
-        <v>37.19253002768617</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>94.98016339506191</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>26.94897448157494</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>56.57812019574367</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489243886511911</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.253993723259</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.489243886511911</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
